--- a/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS6500_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS6500_SW2.xlsx
@@ -941,7 +941,7 @@
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>Air-Way FF6500 (s24, double-pass 2026-10-15, parts.air-way.com/api/series/24, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p9 FS6500-08-08-FG (ORFS-p009-t01); FORGED part: Air-Way NON-forged row FF6500-8-8-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length = gen_straight2 FSM_MEAS (Brennan FS2403-08-08); on the forged legs the thread major runs to the end length and steps down to the hex flats (Brennan FS6500 / FS6801 / FS2701-08 forged legs) - the end stands proud of the flats; hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); female face-seal SWIVEL leg (Brennan FS6500-08-08-FG, SAE J1453): leg length = the row L21, crossing -&gt; the stem's flat SEAL face (= Brennan AAA; measured - the nut face is 0.433 further out at -08, PLAN.md had read L21 as the nut face); nut hex = the row SHEX (= FF318 S, Q-FS-NUT) over the measured hex length; rear skirt cone, skirt, nut rear face, neck and body face measured; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink and 45deg relief, a cone to the stem head, stem head to the seal face (measured, -08 only - other sizes need BRENNAN_FS6500-NN-NN-FG); NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way FF6500 (s24, double-pass 2026-10-15, parts.air-way.com/api/series/24, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p9 FS6500-08-08-FG (ORFS-p009-t01); FORGED part: Air-Way NON-forged row FF6500-8-8-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); female face-seal SWIVEL leg (Brennan FS6500-08-08-FG, SAE J1453): leg length = the row L21, crossing -&gt; the stem's flat SEAL face (= Brennan AAA; measured - the nut face is 0.433 further out at -08, PLAN.md had read L21 as the nut face); nut hex = the row SHEX (= FF318 S, Q-FS-NUT) over the measured hex length; rear skirt cone, skirt, nut rear face, neck and body face measured; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink and 45deg relief, a cone to the stem head, stem head to the seal face (measured, -08 only - other sizes need BRENNAN_FS6500-NN-NN-FG); NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">

--- a/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS6500_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS6500_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM2"/>
+  <dimension ref="A1:BM4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -952,6 +952,440 @@
       <c r="BM2" t="inlineStr">
         <is>
           <t>FS6500-08-08-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FS6500-06-06-FG</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="F3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.46765</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="W3" t="n">
+        <v>45</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1.525</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.6198399999999999</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.525</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0.43251</v>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>FS6500-06-06-FG</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>ORFS 90 deg Male Face Seal x Female Face Seal Swivel Elbow, 11/16-16 UN (male O-ring face seal, SAE J1453) x 11/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>FS6500</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>11/16-16 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>11/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>Air-Way FF6500 (s24, double-pass 2026-10-15, parts.air-way.com/api/series/24, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p9 FS6500-06-06-FG (ORFS-p009-t01); FORGED part: Air-Way NON-forged row FF6500-6-6-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); female face-seal SWIVEL leg (Brennan FS6500-08-08-FG, SAE J1453): leg length = the row L21, crossing -&gt; the stem's flat SEAL face (= Brennan AAA; measured - the nut face is 0.433 further out at -08, PLAN.md had read L21 as the nut face); nut hex = the row SHEX (= FF318 S, Q-FS-NUT) over the measured hex length; rear skirt cone, skirt, nut rear face, neck and body face measured; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink and 45deg relief, a cone to the stem head, stem head to the seal face (measured, -08 only - other sizes need BRENNAN_FS6500-NN-NN-FG); NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged FF6500-6-6-O = Brennan forged FS6500-06-06-FG p9 on every compared cell (M LGTH ~ L7, AAA LGTH ~ L21, C HEX ~ S, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6500 is used only where Brennan FS6500-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5575 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are single-source (Brennan pilot STEPs) | leg 2: the corner puck (radius 0.433) reaches 0.018 past the swivel body face (0.415) but stays inside the neck (max 0.124 off the axis vs neck radius 0.261) - as on the Brennan 6502-08-08-FG / 1503-08-08-FG forgings; leg 2 hex arm 0.415 barely clears the corner puck (radius 0.433)</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>FS6500-06-06-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FS6500-08-06-FG</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.45725</v>
+      </c>
+      <c r="F4" t="n">
+        <v>45</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.2125</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.46881</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="W4" t="n">
+        <v>45</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1.705</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.45725</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.6198399999999999</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.705</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0.21601</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.43251</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>FS6500-08-06-FG</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>ORFS 90 deg Male Face Seal x Female Face Seal Swivel Elbow, 13/16-16 UN (male O-ring face seal, SAE J1453) x 11/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>FS6500</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>13/16-16 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>11/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] not built: forged part where Air-Way and Brennan do not match on every cell (user 2026-10-15: the rest stay MISSING) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L7@DRIVE: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-08-06-FG col "M LGTH" = "1.10" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 230.3, page verified True) [Brennan = yes 2026-10-18] - FS leg face -&gt; crossing; mapping: same-table check: 5/5 rows with an Air-Way value agree to rounding; L21@DRIVE: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-08-06-FG col "AAA LGTH" = "1.33" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 230.3, page verified True) [Brennan = yes 2026-10-18] - swivel leg crossing -&gt; nut face; mapping: same-table check: 5/5 rows with an Air-Way value agree to rounding; SHEX@HEX: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-08-06-FG col "C HEX" = "0.812" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 230.3, page verified True) [Brennan = yes 2026-10-18] - swivel nut hex; mapping: same-table check: 5/5 rows with an Air-Way value agree to rounding; Q-FS-NUT: = Air-Way FF318-6 S 0.81 to rounding; S2HEX@HEX: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-08-06-FG col "JJ FLATS" = "0.750" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 230.3, page verified True) [Brennan = yes 2026-10-18] - forged flats; mapping: same-table check: 5/5 rows with an Air-Way value agree to rounding; THDMAJ_D_1@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -08 = 0.8125 (PLAN.md s2 FS_THR / the -08 thread of every staged ORFS row); = Brennan "A THREAD" "13/16-16" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_D_2@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -06 = 0.6875 (PLAN.md s2 FS_THR / the -06 thread of every staged ORFS row); = Brennan "B THREAD" "11/16-16" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D_1: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-08-06-FG col "A THREAD" "13/16-16" in the table's format; $PRP@Thread_D_2: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-08-06-FG col "B THREAD" "11/16-16" in the table's format; D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS6500: FSM -08 bore on 1 Air-Way row(s): 0.37 (unanimous) [Air-Way, not Brennan]; D19@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS6500: FSSW -06 bore on 1 Air-Way row(s): 0.26 (unanimous) [Air-Way, not Brennan] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); female face-seal SWIVEL leg (Brennan FS6500-08-08-FG, SAE J1453): leg length = the row L21, crossing -&gt; the stem's flat SEAL face (= Brennan AAA; measured - the nut face is 0.433 further out at -08, PLAN.md had read L21 as the nut face); nut hex = the row SHEX (= FF318 S, Q-FS-NUT) over the measured hex length; rear skirt cone, skirt, nut rear face, neck and body face measured; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink and 45deg relief, a cone to the stem head, stem head to the seal face (measured, -08 only - other sizes need BRENNAN_FS6500-NN-NN-FG); NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>forged (-FG): Brennan p9 prints it but Air-Way has no non-forged row - Brennan-only stays MISSING | forged (-FG): the Air-Way NON-forged series FF6500 is used only where Brennan FS6500-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5577 (no dimensions) | 2026-10-18 Brennan = yes (wave 3 ORFS, staged, not shipped): sizes from Brennan ORFS p9 FS6500-08-06-FG ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); threads by dash (end library)</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>FS6500-08-06-FG</t>
         </is>
       </c>
     </row>

--- a/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS6500_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS6500_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM4"/>
+  <dimension ref="A1:BL4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,215 +524,210 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>FSW2_CSANG@LEG2</t>
+          <t>FSW2_MINR@LEG2</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>FSW2_MINR@LEG2</t>
+          <t>FSW2_THDL@LEG2</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>FSW2_THDL@LEG2</t>
+          <t>FSW2_RELANG@LEG2</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>FSW2_RELANG@LEG2</t>
+          <t>FSW2_RELR@LEG2</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>FSW2_RELR@LEG2</t>
+          <t>FSW2_STEMR@LEG2</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>FSW2_STEMR@LEG2</t>
+          <t>FSW2_HEADL@LEG2</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>FSW2_HEADL@LEG2</t>
+          <t>NUTHEX2@NUTHEX2</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>NUTHEX2@NUTHEX2</t>
+          <t>DEPTH@NUTCUT2</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>DEPTH@NUTCUT2</t>
+          <t>D1@BORE1</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>D1@BORE1</t>
+          <t>DEPTH@BORECUT1</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>DEPTH@BORECUT1</t>
+          <t>D2@BORE2</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>D2@BORE2</t>
+          <t>DEPTH@BORECUT2</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>DEPTH@BORECUT2</t>
+          <t>THDDIA@THD_End1</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>THDDIA@THD_End1</t>
+          <t>THDPITCH@THD_End1</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>THDPITCH@THD_End1</t>
+          <t>DEPTH@THD_End1</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>DEPTH@THD_End1</t>
+          <t>Profile_Height@THD_End1_PROF</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>Profile_Height@THD_End1_PROF</t>
+          <t>Profile_Land@THD_End1_PROF</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>Profile_Land@THD_End1_PROF</t>
+          <t>THDPITCH@THD_End1_PROF</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>THDPITCH@THD_End1_PROF</t>
+          <t>HELIXDIA@HELIXSK_2</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>HELIXDIA@HELIXSK_2</t>
+          <t>HEIGHT@HELIX_2</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>HEIGHT@HELIX_2</t>
+          <t>PITCH@HELIX_2</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>PITCH@HELIX_2</t>
+          <t>PROF_R@THDPROF_2</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>PROF_R@THDPROF_2</t>
+          <t>APEXR@THDPROF_2</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>APEXR@THDPROF_2</t>
+          <t>PROF_AX@THDPROF_2</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>PROF_AX@THDPROF_2</t>
+          <t>HEXAF@HEX1</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>HEXAF@HEX1</t>
+          <t>HEXL@HEX1_BODY</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>HEXL@HEX1_BODY</t>
+          <t>HEXAF@HEX2</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>HEXAF@HEX2</t>
+          <t>HEXL@HEX2_BODY</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>HEXL@HEX2_BODY</t>
+          <t>PUCK_HB@PUCK</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>PUCK_HB@PUCK</t>
+          <t>PUCK_HT@PUCK</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>PUCK_HT@PUCK</t>
+          <t>PUCK_R1B@PUCK</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>PUCK_R1B@PUCK</t>
+          <t>PUCK_R1T@PUCK</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>PUCK_R1T@PUCK</t>
+          <t>PUCK_XC@PUCK</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>PUCK_XC@PUCK</t>
+          <t>$PRP@PartNo</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>$PRP@PartNo</t>
+          <t>$PRP@Description</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>$PRP@Description</t>
+          <t>$PRP@GeometryRoot</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>$PRP@GeometryRoot</t>
+          <t>$PRP@End1_Thread</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>$PRP@End1_Thread</t>
+          <t>$PRP@End2_Thread</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>$PRP@End2_Thread</t>
+          <t>$PRP@DataStatus</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>$PRP@DataStatus</t>
+          <t>$PRP@AxialSource</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>$PRP@AxialSource</t>
+          <t>$COMMENT</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
-        <is>
-          <t>$COMMENT</t>
-        </is>
-      </c>
-      <c r="BM1" t="inlineStr">
         <is>
           <t>$PRP@OMiSKU</t>
         </is>
@@ -808,148 +803,145 @@
         <v>0.4095</v>
       </c>
       <c r="W2" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="Y2" t="n">
         <v>45</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Z2" t="n">
+        <v>0.4165</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.3725</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.923</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.45725</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.7448399999999999</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.4059</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AR2" t="n">
         <v>0.37242</v>
       </c>
-      <c r="Y2" t="n">
-        <v>0.36882</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.4165</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.3725</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.197</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0.482</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="AI2" t="n">
+      <c r="AS2" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="AT2" t="n">
         <v>1.923</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0.45725</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0.03383</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0.01562</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0.7448399999999999</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0.4059</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0.37242</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0.40625</v>
-      </c>
       <c r="AU2" t="n">
-        <v>1.923</v>
+        <v>0.75</v>
       </c>
       <c r="AV2" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="AW2" t="n">
         <v>0.75</v>
       </c>
-      <c r="AW2" t="n">
-        <v>0.596</v>
-      </c>
       <c r="AX2" t="n">
-        <v>0.75</v>
+        <v>0.635</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.635</v>
+        <v>0.375</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.375</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.375</v>
+        <v>0.21601</v>
       </c>
       <c r="BB2" t="n">
         <v>0.21601</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.21601</v>
-      </c>
-      <c r="BD2" t="n">
         <v>0.43251</v>
       </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>FS6500-08-08-FG</t>
+        </is>
+      </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>FS6500-08-08-FG</t>
+          <t>ORFS 90 deg Male Face Seal x Female Face Seal Swivel Elbow, 13/16-16 UN (male O-ring face seal, SAE J1453) x 13/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>ORFS 90 deg Male Face Seal x Female Face Seal Swivel Elbow, 13/16-16 UN (male O-ring face seal, SAE J1453) x 13/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>FS6500</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>FS6500</t>
+          <t>13/16-16 UN (male O-ring face seal, SAE J1453)</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>13/16-16 UN (male O-ring face seal, SAE J1453)</t>
+          <t>13/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>13/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>Air-Way FF6500 (s24, double-pass 2026-10-15, parts.air-way.com/api/series/24, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p9 FS6500-08-08-FG (ORFS-p009-t01); FORGED part: Air-Way NON-forged row FF6500-8-8-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); female face-seal SWIVEL leg (Brennan FS6500-08-08-FG, SAE J1453): leg length = the row L21, crossing -&gt; the stem's flat SEAL face (= Brennan AAA; measured - the nut face is 0.433 further out at -08, PLAN.md had read L21 as the nut face); nut hex = the row SHEX (= FF318 S, Q-FS-NUT) over the measured hex length; rear skirt cone, skirt, nut rear face, neck and body face measured; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink and 45deg relief, a cone to the stem head, stem head to the seal face (measured, -08 only - other sizes need BRENNAN_FS6500-NN-NN-FG); NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>Air-Way FF6500 (s24, double-pass 2026-10-15, parts.air-way.com/api/series/24, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p9 FS6500-08-08-FG (ORFS-p009-t01); FORGED part: Air-Way NON-forged row FF6500-8-8-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); female face-seal SWIVEL leg (Brennan FS6500-08-08-FG, SAE J1453): leg length = the row L21, crossing -&gt; the stem's flat SEAL face (= Brennan AAA; measured - the nut face is 0.433 further out at -08, PLAN.md had read L21 as the nut face); nut hex = the row SHEX (= FF318 S, Q-FS-NUT) over the measured hex length; rear skirt cone, skirt, nut rear face, neck and body face measured; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink and 45deg relief, a cone to the stem head, stem head to the seal face (measured, -08 only - other sizes need BRENNAN_FS6500-NN-NN-FG); NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); each leg bore runs from its face to the axis crossing</t>
+          <t>forged (-FG): Air-Way non-forged FF6500-8-8-O = Brennan forged FS6500-08-08-FG p9 on every compared cell (M LGTH ~ L7, AAA LGTH ~ L21, C HEX ~ S, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6500 is used only where Brennan FS6500-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5578 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are single-source (Brennan pilot STEPs)</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
-        <is>
-          <t>forged (-FG): Air-Way non-forged FF6500-8-8-O = Brennan forged FS6500-08-08-FG p9 on every compared cell (M LGTH ~ L7, AAA LGTH ~ L21, C HEX ~ S, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6500 is used only where Brennan FS6500-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5578 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are single-source (Brennan pilot STEPs)</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
         <is>
           <t>FS6500-08-08-FG</t>
         </is>
@@ -1025,148 +1017,145 @@
         <v>0.3465</v>
       </c>
       <c r="W3" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="Y3" t="n">
         <v>45</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.525</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.6198399999999999</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AR3" t="n">
         <v>0.30992</v>
       </c>
-      <c r="Y3" t="n">
-        <v>0.30432</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.177</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0.392</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AI3" t="n">
+      <c r="AS3" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="AT3" t="n">
         <v>1.525</v>
       </c>
-      <c r="AJ3" t="n">
-        <v>0.6875</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0.39425</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0.03383</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0.01562</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0.6198399999999999</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0.3409</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0.30992</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0.34375</v>
-      </c>
       <c r="AU3" t="n">
-        <v>1.525</v>
+        <v>0.75</v>
       </c>
       <c r="AV3" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="AW3" t="n">
         <v>0.75</v>
       </c>
-      <c r="AW3" t="n">
-        <v>0.539</v>
-      </c>
       <c r="AX3" t="n">
-        <v>0.75</v>
+        <v>0.415</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.415</v>
+        <v>0.375</v>
       </c>
       <c r="AZ3" t="n">
         <v>0.375</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.375</v>
+        <v>0.21601</v>
       </c>
       <c r="BB3" t="n">
         <v>0.21601</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.21601</v>
-      </c>
-      <c r="BD3" t="n">
         <v>0.43251</v>
       </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>FS6500-06-06-FG</t>
+        </is>
+      </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>FS6500-06-06-FG</t>
+          <t>ORFS 90 deg Male Face Seal x Female Face Seal Swivel Elbow, 11/16-16 UN (male O-ring face seal, SAE J1453) x 11/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>ORFS 90 deg Male Face Seal x Female Face Seal Swivel Elbow, 11/16-16 UN (male O-ring face seal, SAE J1453) x 11/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>FS6500</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>FS6500</t>
+          <t>11/16-16 UN (male O-ring face seal, SAE J1453)</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>11/16-16 UN (male O-ring face seal, SAE J1453)</t>
+          <t>11/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>11/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>Air-Way FF6500 (s24, double-pass 2026-10-15, parts.air-way.com/api/series/24, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p9 FS6500-06-06-FG (ORFS-p009-t01); FORGED part: Air-Way NON-forged row FF6500-6-6-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); female face-seal SWIVEL leg (Brennan FS6500-08-08-FG, SAE J1453): leg length = the row L21, crossing -&gt; the stem's flat SEAL face (= Brennan AAA; measured - the nut face is 0.433 further out at -08, PLAN.md had read L21 as the nut face); nut hex = the row SHEX (= FF318 S, Q-FS-NUT) over the measured hex length; rear skirt cone, skirt, nut rear face, neck and body face measured; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink and 45deg relief, a cone to the stem head, stem head to the seal face (measured, -08 only - other sizes need BRENNAN_FS6500-NN-NN-FG); NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>Air-Way FF6500 (s24, double-pass 2026-10-15, parts.air-way.com/api/series/24, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p9 FS6500-06-06-FG (ORFS-p009-t01); FORGED part: Air-Way NON-forged row FF6500-6-6-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); female face-seal SWIVEL leg (Brennan FS6500-08-08-FG, SAE J1453): leg length = the row L21, crossing -&gt; the stem's flat SEAL face (= Brennan AAA; measured - the nut face is 0.433 further out at -08, PLAN.md had read L21 as the nut face); nut hex = the row SHEX (= FF318 S, Q-FS-NUT) over the measured hex length; rear skirt cone, skirt, nut rear face, neck and body face measured; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink and 45deg relief, a cone to the stem head, stem head to the seal face (measured, -08 only - other sizes need BRENNAN_FS6500-NN-NN-FG); NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); each leg bore runs from its face to the axis crossing</t>
+          <t>forged (-FG): Air-Way non-forged FF6500-6-6-O = Brennan forged FS6500-06-06-FG p9 on every compared cell (M LGTH ~ L7, AAA LGTH ~ L21, C HEX ~ S, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6500 is used only where Brennan FS6500-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5575 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are single-source (Brennan pilot STEPs) | leg 2: the corner puck (radius 0.433) reaches 0.018 past the swivel body face (0.415) but stays inside the neck (max 0.124 off the axis vs neck radius 0.261) - as on the Brennan 6502-08-08-FG / 1503-08-08-FG forgings; leg 2 hex arm 0.415 barely clears the corner puck (radius 0.433)</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
-        <is>
-          <t>forged (-FG): Air-Way non-forged FF6500-6-6-O = Brennan forged FS6500-06-06-FG p9 on every compared cell (M LGTH ~ L7, AAA LGTH ~ L21, C HEX ~ S, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6500 is used only where Brennan FS6500-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5575 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are single-source (Brennan pilot STEPs) | leg 2: the corner puck (radius 0.433) reaches 0.018 past the swivel body face (0.415) but stays inside the neck (max 0.124 off the axis vs neck radius 0.261) - as on the Brennan 6502-08-08-FG / 1503-08-08-FG forgings; leg 2 hex arm 0.415 barely clears the corner puck (radius 0.433)</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
         <is>
           <t>FS6500-06-06-FG</t>
         </is>
@@ -1242,148 +1231,145 @@
         <v>0.3465</v>
       </c>
       <c r="W4" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="Y4" t="n">
         <v>45</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Z4" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.705</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.45725</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.6198399999999999</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AR4" t="n">
         <v>0.30992</v>
       </c>
-      <c r="Y4" t="n">
-        <v>0.30432</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0.177</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0.8120000000000001</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0.392</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AI4" t="n">
+      <c r="AS4" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="AT4" t="n">
         <v>1.705</v>
       </c>
-      <c r="AJ4" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0.45725</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0.03383</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0.01562</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0.6198399999999999</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0.3409</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0.30992</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0.34375</v>
-      </c>
       <c r="AU4" t="n">
-        <v>1.705</v>
+        <v>0.75</v>
       </c>
       <c r="AV4" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="AW4" t="n">
         <v>0.75</v>
       </c>
-      <c r="AW4" t="n">
-        <v>0.596</v>
-      </c>
       <c r="AX4" t="n">
-        <v>0.75</v>
+        <v>0.595</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.595</v>
+        <v>0.375</v>
       </c>
       <c r="AZ4" t="n">
         <v>0.375</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.375</v>
+        <v>0.21601</v>
       </c>
       <c r="BB4" t="n">
         <v>0.21601</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.21601</v>
-      </c>
-      <c r="BD4" t="n">
         <v>0.43251</v>
       </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>FS6500-08-06-FG</t>
+        </is>
+      </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>FS6500-08-06-FG</t>
+          <t>ORFS 90 deg Male Face Seal x Female Face Seal Swivel Elbow, 13/16-16 UN (male O-ring face seal, SAE J1453) x 11/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>ORFS 90 deg Male Face Seal x Female Face Seal Swivel Elbow, 13/16-16 UN (male O-ring face seal, SAE J1453) x 11/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>FS6500</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>FS6500</t>
+          <t>13/16-16 UN (male O-ring face seal, SAE J1453)</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>13/16-16 UN (male O-ring face seal, SAE J1453)</t>
+          <t>11/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>11/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>[BRENNAN-ONLY 2026-10-18] not built: forged part where Air-Way and Brennan do not match on every cell (user 2026-10-15: the rest stay MISSING) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L7@DRIVE: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-08-06-FG col "M LGTH" = "1.10" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 230.3, page verified True) [Brennan = yes 2026-10-18] - FS leg face -&gt; crossing; mapping: same-table check: 5/5 rows with an Air-Way value agree to rounding; L21@DRIVE: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-08-06-FG col "AAA LGTH" = "1.33" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 230.3, page verified True) [Brennan = yes 2026-10-18] - swivel leg crossing -&gt; nut face; mapping: same-table check: 5/5 rows with an Air-Way value agree to rounding; SHEX@HEX: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-08-06-FG col "C HEX" = "0.812" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 230.3, page verified True) [Brennan = yes 2026-10-18] - swivel nut hex; mapping: same-table check: 5/5 rows with an Air-Way value agree to rounding; Q-FS-NUT: = Air-Way FF318-6 S 0.81 to rounding; S2HEX@HEX: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-08-06-FG col "JJ FLATS" = "0.750" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 230.3, page verified True) [Brennan = yes 2026-10-18] - forged flats; mapping: same-table check: 5/5 rows with an Air-Way value agree to rounding; THDMAJ_D_1@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -08 = 0.8125 (PLAN.md s2 FS_THR / the -08 thread of every staged ORFS row); = Brennan "A THREAD" "13/16-16" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_D_2@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -06 = 0.6875 (PLAN.md s2 FS_THR / the -06 thread of every staged ORFS row); = Brennan "B THREAD" "11/16-16" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D_1: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-08-06-FG col "A THREAD" "13/16-16" in the table's format; $PRP@Thread_D_2: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-08-06-FG col "B THREAD" "11/16-16" in the table's format; D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS6500: FSM -08 bore on 1 Air-Way row(s): 0.37 (unanimous) [Air-Way, not Brennan]; D19@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS6500: FSSW -06 bore on 1 Air-Way row(s): 0.26 (unanimous) [Air-Way, not Brennan] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); female face-seal SWIVEL leg (Brennan FS6500-08-08-FG, SAE J1453): leg length = the row L21, crossing -&gt; the stem's flat SEAL face (= Brennan AAA; measured - the nut face is 0.433 further out at -08, PLAN.md had read L21 as the nut face); nut hex = the row SHEX (= FF318 S, Q-FS-NUT) over the measured hex length; rear skirt cone, skirt, nut rear face, neck and body face measured; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink and 45deg relief, a cone to the stem head, stem head to the seal face (measured, -08 only - other sizes need BRENNAN_FS6500-NN-NN-FG); NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>[BRENNAN-ONLY 2026-10-18] not built: forged part where Air-Way and Brennan do not match on every cell (user 2026-10-15: the rest stay MISSING) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L7@DRIVE: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-08-06-FG col "M LGTH" = "1.10" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 230.3, page verified True) [Brennan = yes 2026-10-18] - FS leg face -&gt; crossing; mapping: same-table check: 5/5 rows with an Air-Way value agree to rounding; L21@DRIVE: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-08-06-FG col "AAA LGTH" = "1.33" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 230.3, page verified True) [Brennan = yes 2026-10-18] - swivel leg crossing -&gt; nut face; mapping: same-table check: 5/5 rows with an Air-Way value agree to rounding; SHEX@HEX: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-08-06-FG col "C HEX" = "0.812" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 230.3, page verified True) [Brennan = yes 2026-10-18] - swivel nut hex; mapping: same-table check: 5/5 rows with an Air-Way value agree to rounding; Q-FS-NUT: = Air-Way FF318-6 S 0.81 to rounding; S2HEX@HEX: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-08-06-FG col "JJ FLATS" = "0.750" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 230.3, page verified True) [Brennan = yes 2026-10-18] - forged flats; mapping: same-table check: 5/5 rows with an Air-Way value agree to rounding; THDMAJ_D_1@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -08 = 0.8125 (PLAN.md s2 FS_THR / the -08 thread of every staged ORFS row); = Brennan "A THREAD" "13/16-16" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_D_2@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -06 = 0.6875 (PLAN.md s2 FS_THR / the -06 thread of every staged ORFS row); = Brennan "B THREAD" "11/16-16" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D_1: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-08-06-FG col "A THREAD" "13/16-16" in the table's format; $PRP@Thread_D_2: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-08-06-FG col "B THREAD" "11/16-16" in the table's format; D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS6500: FSM -08 bore on 1 Air-Way row(s): 0.37 (unanimous) [Air-Way, not Brennan]; D19@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS6500: FSSW -06 bore on 1 Air-Way row(s): 0.26 (unanimous) [Air-Way, not Brennan] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); female face-seal SWIVEL leg (Brennan FS6500-08-08-FG, SAE J1453): leg length = the row L21, crossing -&gt; the stem's flat SEAL face (= Brennan AAA; measured - the nut face is 0.433 further out at -08, PLAN.md had read L21 as the nut face); nut hex = the row SHEX (= FF318 S, Q-FS-NUT) over the measured hex length; rear skirt cone, skirt, nut rear face, neck and body face measured; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink and 45deg relief, a cone to the stem head, stem head to the seal face (measured, -08 only - other sizes need BRENNAN_FS6500-NN-NN-FG); NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); each leg bore runs from its face to the axis crossing</t>
+          <t>forged (-FG): Brennan p9 prints it but Air-Way has no non-forged row - Brennan-only stays MISSING | forged (-FG): the Air-Way NON-forged series FF6500 is used only where Brennan FS6500-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5577 (no dimensions) | 2026-10-18 Brennan = yes (wave 3 ORFS, staged, not shipped): sizes from Brennan ORFS p9 FS6500-08-06-FG ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); threads by dash (end library)</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
-        <is>
-          <t>forged (-FG): Brennan p9 prints it but Air-Way has no non-forged row - Brennan-only stays MISSING | forged (-FG): the Air-Way NON-forged series FF6500 is used only where Brennan FS6500-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5577 (no dimensions) | 2026-10-18 Brennan = yes (wave 3 ORFS, staged, not shipped): sizes from Brennan ORFS p9 FS6500-08-06-FG ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); threads by dash (end library)</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
         <is>
           <t>FS6500-08-06-FG</t>
         </is>
